--- a/output/pdf_financials_xlsx/OPTI.xlsx
+++ b/output/pdf_financials_xlsx/OPTI.xlsx
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5.194548</v>
+        <v>-5.194548</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-6.035859</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5.194548</v>
+        <v>-5.194548</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-6.035859</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5.194548</v>
+        <v>-5.194548</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-6.035859</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5.194548</v>
+        <v>-5.194548</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-6.035859</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5.924108</v>
+        <v>-4.464988</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-5.167912</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>3271.415397019113</v>
+        <v>-2465.659047860973</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>-1325.615493138387</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>2868.537222440043</v>
+        <v>-2868.537222440043</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>-1548.251635244325</v>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.157756</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.028102</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.120398</v>
       </c>
     </row>
     <row r="93">
@@ -3336,7 +3336,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -3712,7 +3716,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>2.157756</v>
       </c>
@@ -6995,7 +7003,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>5.194548</v>
+        <v>-5.194548</v>
       </c>
       <c r="F142" s="5" t="n">
         <v>-6.035859</v>

--- a/output/pdf_financials_xlsx/OPTI.xlsx
+++ b/output/pdf_financials_xlsx/OPTI.xlsx
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.901852</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.749376</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.185684</v>
       </c>
     </row>
     <row r="65">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.160359</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.173007</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.205296</v>
       </c>
     </row>
     <row r="68">
